--- a/Купол Энергетики/Сonsumption plan Data_frame_2.xlsx
+++ b/Купол Энергетики/Сonsumption plan Data_frame_2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -180,6 +180,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -188,10 +192,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,44 +474,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L102"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="6" width="8.88671875" style="5"/>
-    <col min="7" max="7" width="12.21875" style="5" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="23.44140625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="17.6640625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="3" width="8.90625" style="1"/>
+    <col min="4" max="6" width="8.90625" style="5"/>
+    <col min="7" max="7" width="12.1796875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="23.453125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="17.6328125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="16.6328125" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7" t="s">
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="10"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -546,7 +546,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>ROW()-2</f>
         <v>1</v>
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6">
         <v>30</v>
@@ -577,7 +577,7 @@
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <f t="shared" ref="A4:A67" si="0">ROW()-2</f>
         <v>2</v>
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D4" s="6">
         <v>24</v>
@@ -608,7 +608,7 @@
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -617,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6">
         <v>39</v>
@@ -639,7 +639,7 @@
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6">
         <v>34</v>
@@ -670,7 +670,7 @@
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D7" s="6">
         <v>39</v>
@@ -701,7 +701,7 @@
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D8" s="6">
         <v>42</v>
@@ -732,7 +732,7 @@
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -741,7 +741,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D9" s="6">
         <v>32</v>
@@ -763,7 +763,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D10" s="6">
         <v>49</v>
@@ -794,7 +794,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D11" s="6">
         <v>46</v>
@@ -825,7 +825,7 @@
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D12" s="6">
         <v>58</v>
@@ -856,7 +856,7 @@
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D13" s="6">
         <v>59</v>
@@ -887,7 +887,7 @@
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -896,7 +896,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="3">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D14" s="6">
         <v>47</v>
@@ -918,7 +918,7 @@
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -927,7 +927,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="3">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D15" s="6">
         <v>49</v>
@@ -949,7 +949,7 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -958,7 +958,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="3">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D16" s="6">
         <v>57</v>
@@ -980,7 +980,7 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -989,7 +989,7 @@
         <v>26</v>
       </c>
       <c r="C17" s="3">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D17" s="6">
         <v>52</v>
@@ -1011,7 +1011,7 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1020,7 +1020,7 @@
         <v>26</v>
       </c>
       <c r="C18" s="3">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D18" s="6">
         <v>66</v>
@@ -1042,7 +1042,7 @@
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1051,7 +1051,7 @@
         <v>35</v>
       </c>
       <c r="C19" s="3">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D19" s="6">
         <v>65</v>
@@ -1073,7 +1073,7 @@
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1082,7 +1082,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="3">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="D20" s="6">
         <v>58</v>
@@ -1104,7 +1104,7 @@
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <f>ROW()-2</f>
         <v>19</v>
@@ -1113,7 +1113,7 @@
         <v>47</v>
       </c>
       <c r="C21" s="3">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D21" s="6">
         <v>70</v>
@@ -1135,7 +1135,7 @@
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1144,7 +1144,7 @@
         <v>45</v>
       </c>
       <c r="C22" s="3">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D22" s="6">
         <v>72</v>
@@ -1166,7 +1166,7 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1175,7 +1175,7 @@
         <v>48</v>
       </c>
       <c r="C23" s="3">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="D23" s="6">
         <v>79</v>
@@ -1197,7 +1197,7 @@
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1206,7 +1206,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="3">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D24" s="6">
         <v>75</v>
@@ -1228,7 +1228,7 @@
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1237,7 +1237,7 @@
         <v>44</v>
       </c>
       <c r="C25" s="3">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D25" s="6">
         <v>69</v>
@@ -1259,7 +1259,7 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1268,7 +1268,7 @@
         <v>48</v>
       </c>
       <c r="C26" s="3">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="D26" s="6">
         <v>82</v>
@@ -1290,7 +1290,7 @@
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1299,7 +1299,7 @@
         <v>52</v>
       </c>
       <c r="C27" s="3">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="D27" s="6">
         <v>74</v>
@@ -1321,131 +1321,131 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C28" s="3">
-        <v>73</v>
-      </c>
-      <c r="D28" s="10">
+        <v>35</v>
+      </c>
+      <c r="D28" s="7">
         <v>87</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="7">
         <v>43</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="7">
         <v>29</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="7">
         <v>62</v>
       </c>
-      <c r="H28" s="10">
-        <v>0</v>
-      </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H28" s="7">
+        <v>0</v>
+      </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C29" s="3">
-        <v>75</v>
-      </c>
-      <c r="D29" s="10">
+        <v>35</v>
+      </c>
+      <c r="D29" s="7">
         <v>78</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="7">
         <v>45</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="7">
         <v>29</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="7">
         <v>61</v>
       </c>
-      <c r="H29" s="10">
-        <v>0</v>
-      </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H29" s="7">
+        <v>0</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C30" s="3">
-        <v>86</v>
-      </c>
-      <c r="D30" s="10">
+        <v>35</v>
+      </c>
+      <c r="D30" s="7">
         <v>74</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="7">
         <v>47</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="7">
         <v>43</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="7">
         <v>56</v>
       </c>
-      <c r="H30" s="10">
-        <v>0</v>
-      </c>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H30" s="7">
+        <v>0</v>
+      </c>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="3">
-        <v>87</v>
-      </c>
-      <c r="D31" s="10">
+        <v>35</v>
+      </c>
+      <c r="D31" s="7">
         <v>85</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="7">
         <v>55</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="7">
         <v>30</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="7">
         <v>55</v>
       </c>
-      <c r="H31" s="10">
-        <v>0</v>
-      </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H31" s="7">
+        <v>0</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1454,29 +1454,29 @@
         <v>66</v>
       </c>
       <c r="C32" s="3">
-        <v>91</v>
-      </c>
-      <c r="D32" s="10">
+        <v>35</v>
+      </c>
+      <c r="D32" s="7">
         <v>96</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="7">
         <v>52</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="7">
         <v>29</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="7">
         <v>60</v>
       </c>
-      <c r="H32" s="10">
-        <v>0</v>
-      </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H32" s="7">
+        <v>0</v>
+      </c>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1485,29 +1485,29 @@
         <v>58</v>
       </c>
       <c r="C33" s="3">
-        <v>87</v>
-      </c>
-      <c r="D33" s="10">
+        <v>35</v>
+      </c>
+      <c r="D33" s="7">
         <v>93</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="7">
         <v>58</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="7">
         <v>29</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="7">
         <v>63</v>
       </c>
-      <c r="H33" s="10">
-        <v>0</v>
-      </c>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H33" s="7">
+        <v>0</v>
+      </c>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -1516,29 +1516,29 @@
         <v>57</v>
       </c>
       <c r="C34" s="3">
-        <v>83</v>
-      </c>
-      <c r="D34" s="10">
+        <v>35</v>
+      </c>
+      <c r="D34" s="7">
         <v>85</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="7">
         <v>60</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="7">
         <v>39</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="7">
         <v>59</v>
       </c>
-      <c r="H34" s="10">
-        <v>0</v>
-      </c>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H34" s="7">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -1547,29 +1547,29 @@
         <v>56</v>
       </c>
       <c r="C35" s="3">
-        <v>89</v>
-      </c>
-      <c r="D35" s="10">
+        <v>35</v>
+      </c>
+      <c r="D35" s="7">
         <v>83</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="7">
         <v>47</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="7">
         <v>31</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="7">
         <v>57</v>
       </c>
-      <c r="H35" s="10">
-        <v>0</v>
-      </c>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H35" s="7">
+        <v>0</v>
+      </c>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -1578,29 +1578,29 @@
         <v>53</v>
       </c>
       <c r="C36" s="3">
-        <v>81</v>
-      </c>
-      <c r="D36" s="10">
+        <v>28</v>
+      </c>
+      <c r="D36" s="7">
         <v>91</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="7">
         <v>54</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="7">
         <v>30</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="7">
         <v>49</v>
       </c>
-      <c r="H36" s="10">
-        <v>0</v>
-      </c>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H36" s="7">
+        <v>0</v>
+      </c>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -1609,29 +1609,29 @@
         <v>43</v>
       </c>
       <c r="C37" s="3">
-        <v>75</v>
-      </c>
-      <c r="D37" s="10">
+        <v>25</v>
+      </c>
+      <c r="D37" s="7">
         <v>82</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="7">
         <v>44</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="7">
         <v>29</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="7">
         <v>59</v>
       </c>
-      <c r="H37" s="10">
-        <v>0</v>
-      </c>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H37" s="7">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -1640,29 +1640,29 @@
         <v>45</v>
       </c>
       <c r="C38" s="3">
-        <v>78</v>
-      </c>
-      <c r="D38" s="10">
+        <v>24</v>
+      </c>
+      <c r="D38" s="7">
         <v>92</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="7">
         <v>47</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="7">
         <v>34</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="7">
         <v>50</v>
       </c>
-      <c r="H38" s="10">
-        <v>0</v>
-      </c>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H38" s="7">
+        <v>0</v>
+      </c>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -1671,29 +1671,29 @@
         <v>46</v>
       </c>
       <c r="C39" s="3">
-        <v>74</v>
-      </c>
-      <c r="D39" s="10">
+        <v>24</v>
+      </c>
+      <c r="D39" s="7">
         <v>84</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="7">
         <v>57</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="7">
         <v>38</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="7">
         <v>60</v>
       </c>
-      <c r="H39" s="10">
-        <v>0</v>
-      </c>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H39" s="7">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -1702,29 +1702,29 @@
         <v>37</v>
       </c>
       <c r="C40" s="3">
-        <v>75</v>
-      </c>
-      <c r="D40" s="10">
+        <v>24</v>
+      </c>
+      <c r="D40" s="7">
         <v>72</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="7">
         <v>56</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="7">
         <v>46</v>
       </c>
-      <c r="G40" s="10">
+      <c r="G40" s="7">
         <v>54</v>
       </c>
-      <c r="H40" s="10">
-        <v>0</v>
-      </c>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H40" s="7">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -1733,29 +1733,29 @@
         <v>27</v>
       </c>
       <c r="C41" s="3">
-        <v>68</v>
-      </c>
-      <c r="D41" s="10">
+        <v>24</v>
+      </c>
+      <c r="D41" s="7">
         <v>71</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="7">
         <v>46</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="7">
         <v>43</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="7">
         <v>50</v>
       </c>
-      <c r="H41" s="10">
-        <v>0</v>
-      </c>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H41" s="7">
+        <v>0</v>
+      </c>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -1764,29 +1764,29 @@
         <v>21</v>
       </c>
       <c r="C42" s="3">
-        <v>68</v>
-      </c>
-      <c r="D42" s="10">
+        <v>36</v>
+      </c>
+      <c r="D42" s="7">
         <v>76</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="7">
         <v>55</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="7">
         <v>55</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="7">
         <v>61</v>
       </c>
-      <c r="H42" s="10">
-        <v>0</v>
-      </c>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H42" s="7">
+        <v>0</v>
+      </c>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -1795,29 +1795,29 @@
         <v>23</v>
       </c>
       <c r="C43" s="3">
+        <v>36</v>
+      </c>
+      <c r="D43" s="7">
+        <v>76</v>
+      </c>
+      <c r="E43" s="7">
+        <v>42</v>
+      </c>
+      <c r="F43" s="7">
+        <v>36</v>
+      </c>
+      <c r="G43" s="7">
         <v>58</v>
       </c>
-      <c r="D43" s="10">
-        <v>76</v>
-      </c>
-      <c r="E43" s="10">
-        <v>42</v>
-      </c>
-      <c r="F43" s="10">
-        <v>36</v>
-      </c>
-      <c r="G43" s="10">
-        <v>58</v>
-      </c>
-      <c r="H43" s="10">
-        <v>0</v>
-      </c>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H43" s="7">
+        <v>0</v>
+      </c>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -1826,29 +1826,29 @@
         <v>27</v>
       </c>
       <c r="C44" s="3">
-        <v>65</v>
-      </c>
-      <c r="D44" s="10">
+        <v>36</v>
+      </c>
+      <c r="D44" s="7">
         <v>81</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="7">
         <v>47</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="7">
         <v>52</v>
       </c>
-      <c r="G44" s="10">
+      <c r="G44" s="7">
         <v>57</v>
       </c>
-      <c r="H44" s="10">
-        <v>0</v>
-      </c>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H44" s="7">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -1857,29 +1857,29 @@
         <v>27</v>
       </c>
       <c r="C45" s="3">
-        <v>55</v>
-      </c>
-      <c r="D45" s="10">
+        <v>36</v>
+      </c>
+      <c r="D45" s="7">
         <v>64</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="7">
         <v>46</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="7">
         <v>45</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="7">
         <v>52</v>
       </c>
-      <c r="H45" s="10">
-        <v>0</v>
-      </c>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H45" s="7">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -1888,29 +1888,29 @@
         <v>29</v>
       </c>
       <c r="C46" s="3">
-        <v>57</v>
-      </c>
-      <c r="D46" s="10">
+        <v>36</v>
+      </c>
+      <c r="D46" s="7">
         <v>74</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="7">
         <v>48</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="7">
         <v>42</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="7">
         <v>52</v>
       </c>
-      <c r="H46" s="10">
-        <v>0</v>
-      </c>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H46" s="7">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -1921,27 +1921,27 @@
       <c r="C47" s="3">
         <v>47</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="7">
         <v>66</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="7">
         <v>45</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="7">
         <v>49</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="7">
         <v>38</v>
       </c>
-      <c r="H47" s="10">
-        <v>0</v>
-      </c>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H47" s="7">
+        <v>0</v>
+      </c>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -1950,29 +1950,29 @@
         <v>31</v>
       </c>
       <c r="C48" s="3">
-        <v>55</v>
-      </c>
-      <c r="D48" s="10">
+        <v>49</v>
+      </c>
+      <c r="D48" s="7">
         <v>65</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="7">
         <v>57</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="7">
         <v>45</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="7">
         <v>51</v>
       </c>
-      <c r="H48" s="10">
-        <v>0</v>
-      </c>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H48" s="7">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -1981,29 +1981,29 @@
         <v>25</v>
       </c>
       <c r="C49" s="3">
-        <v>46</v>
-      </c>
-      <c r="D49" s="10">
+        <v>49</v>
+      </c>
+      <c r="D49" s="7">
         <v>61</v>
       </c>
-      <c r="E49" s="10">
+      <c r="E49" s="7">
         <v>48</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="7">
         <v>48</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="7">
         <v>49</v>
       </c>
-      <c r="H49" s="10">
-        <v>0</v>
-      </c>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H49" s="7">
+        <v>0</v>
+      </c>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -2014,27 +2014,27 @@
       <c r="C50" s="3">
         <v>39</v>
       </c>
-      <c r="D50" s="10">
+      <c r="D50" s="7">
         <v>58</v>
       </c>
-      <c r="E50" s="10">
+      <c r="E50" s="7">
         <v>47</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="7">
         <v>63</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="7">
         <v>45</v>
       </c>
-      <c r="H50" s="10">
-        <v>0</v>
-      </c>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H50" s="7">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -2045,27 +2045,27 @@
       <c r="C51" s="3">
         <v>37</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="7">
         <v>69</v>
       </c>
-      <c r="E51" s="10">
+      <c r="E51" s="7">
         <v>55</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="7">
         <v>58</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="7">
         <v>50</v>
       </c>
-      <c r="H51" s="10">
-        <v>0</v>
-      </c>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H51" s="7">
+        <v>0</v>
+      </c>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -2076,27 +2076,27 @@
       <c r="C52" s="3">
         <v>41</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="7">
         <v>69</v>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="7">
         <v>50</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="7">
         <v>61</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="7">
         <v>51</v>
       </c>
-      <c r="H52" s="10">
-        <v>0</v>
-      </c>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H52" s="7">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -2127,7 +2127,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -2158,7 +2158,7 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -2189,7 +2189,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -2220,7 +2220,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -2251,7 +2251,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -2282,7 +2282,7 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -2313,7 +2313,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -2344,7 +2344,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -2375,7 +2375,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -2406,7 +2406,7 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -2437,7 +2437,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -2468,7 +2468,7 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -2499,7 +2499,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -2530,7 +2530,7 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -2561,7 +2561,7 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <f t="shared" ref="A68:A102" si="1">ROW()-2</f>
         <v>66</v>
@@ -2592,7 +2592,7 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
         <f t="shared" si="1"/>
         <v>67</v>
@@ -2623,7 +2623,7 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -2654,7 +2654,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -2685,7 +2685,7 @@
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -2716,7 +2716,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -2747,7 +2747,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -2778,7 +2778,7 @@
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -2809,7 +2809,7 @@
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -2840,7 +2840,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -2871,13 +2871,13 @@
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B78" s="3">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C78" s="3">
         <v>7</v>
@@ -2902,13 +2902,13 @@
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B79" s="3">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C79" s="3">
         <v>2</v>
@@ -2933,13 +2933,13 @@
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="B80" s="3">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="C80" s="3">
         <v>2</v>
@@ -2964,13 +2964,13 @@
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B81" s="3">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C81" s="3">
         <v>1</v>
@@ -2995,13 +2995,13 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B82" s="3">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C82" s="3">
         <v>2</v>
@@ -3026,13 +3026,13 @@
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="B83" s="3">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="C83" s="3">
         <v>0</v>
@@ -3057,13 +3057,13 @@
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="B84" s="3">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="C84" s="3">
         <v>8</v>
@@ -3088,13 +3088,13 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
       <c r="B85" s="3">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C85" s="3">
         <v>1</v>
@@ -3119,13 +3119,13 @@
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="B86" s="3">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C86" s="3">
         <v>0</v>
@@ -3150,13 +3150,13 @@
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="B87" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C87" s="3">
         <v>3</v>
@@ -3181,13 +3181,13 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="B88" s="3">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="C88" s="3">
         <v>2</v>
@@ -3212,13 +3212,13 @@
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="B89" s="3">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="C89" s="3">
         <v>0</v>
@@ -3243,13 +3243,13 @@
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="B90" s="3">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="C90" s="3">
         <v>3</v>
@@ -3274,13 +3274,13 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B91" s="3">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C91" s="3">
         <v>4</v>
@@ -3305,13 +3305,13 @@
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B92" s="3">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C92" s="3">
         <v>3</v>
@@ -3336,13 +3336,13 @@
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
       <c r="B93" s="3">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="C93" s="3">
         <v>0</v>
@@ -3367,13 +3367,13 @@
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="B94" s="3">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C94" s="3">
         <v>2</v>
@@ -3398,13 +3398,13 @@
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
       <c r="B95" s="3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C95" s="3">
         <v>0</v>
@@ -3429,7 +3429,7 @@
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -3460,7 +3460,7 @@
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -3491,7 +3491,7 @@
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -3522,7 +3522,7 @@
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -3553,7 +3553,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -3584,7 +3584,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -3615,7 +3615,7 @@
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -3647,7 +3647,7 @@
       <c r="L102" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0cy8wD1xhvVkf4evVFuzuNHBk8wqzUobxIX7fgZdzzKYOeUyH4gusmE+/hOt3GoPwCccmcVzqtO/pKOC8ERcEw==" saltValue="lHxB7A0TB5uTAQIBd+Xwow==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="CC71" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="4">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:G1"/>
